--- a/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Kerala/results/SoIB_summaries.xlsx
@@ -523,13 +523,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>29.3</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -546,7 +546,7 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>57.3</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -580,7 +580,7 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C8">
-        <v>261</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>12</v>
@@ -761,10 +761,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C4">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -810,7 +810,7 @@
         <v>77</v>
       </c>
       <c r="C2">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="D2">
         <v>77</v>
@@ -824,10 +824,10 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>18</v>
